--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1289,6 +1289,1342 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120170109</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79511</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>875805</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7396155</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120170128</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>875926</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7396221</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120170110</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>658</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>876232</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7396328</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120170103</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>876287</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7396347</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120170130</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>876271</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7396332</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120170101</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>876264</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7396337</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120170126</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>875797</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7396161</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120170107</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>876039</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7396234</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>avbarkad tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120170111</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92030</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>876267</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7396323</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120170116</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78262</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>876017</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7396223</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120170129</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>876188</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7396304</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120170132</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>876302</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7396316</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120170104</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hanhivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>875836</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7396192</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134336</v>
+        <v>120134327</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876268</v>
+        <v>876266</v>
       </c>
       <c r="R2" t="n">
-        <v>7396332</v>
+        <v>7396336</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134334</v>
+        <v>120134333</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>875837</v>
+        <v>876265</v>
       </c>
       <c r="R3" t="n">
-        <v>7396182</v>
+        <v>7396339</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134335</v>
+        <v>120134336</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>875839</v>
+        <v>876268</v>
       </c>
       <c r="R4" t="n">
-        <v>7396189</v>
+        <v>7396332</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134327</v>
+        <v>120134334</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876266</v>
+        <v>875837</v>
       </c>
       <c r="R6" t="n">
-        <v>7396336</v>
+        <v>7396182</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134333</v>
+        <v>120134335</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,21 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876265</v>
+        <v>875839</v>
       </c>
       <c r="R7" t="n">
-        <v>7396339</v>
+        <v>7396189</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120170109</v>
+        <v>120170126</v>
       </c>
       <c r="B8" t="n">
-        <v>79511</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,25 +1303,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>875805</v>
+        <v>875797</v>
       </c>
       <c r="R8" t="n">
-        <v>7396155</v>
+        <v>7396161</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170128</v>
+        <v>120170107</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>875926</v>
+        <v>876039</v>
       </c>
       <c r="R9" t="n">
-        <v>7396221</v>
+        <v>7396234</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1469,6 +1469,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170110</v>
+        <v>120170132</v>
       </c>
       <c r="B10" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876232</v>
+        <v>876302</v>
       </c>
       <c r="R10" t="n">
-        <v>7396328</v>
+        <v>7396316</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1597,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170103</v>
+        <v>120170111</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>92030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876287</v>
+        <v>876267</v>
       </c>
       <c r="R11" t="n">
-        <v>7396347</v>
+        <v>7396323</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1699,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170130</v>
+        <v>120170103</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876271</v>
+        <v>876287</v>
       </c>
       <c r="R12" t="n">
-        <v>7396332</v>
+        <v>7396347</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1801,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170101</v>
+        <v>120170130</v>
       </c>
       <c r="B13" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876264</v>
+        <v>876271</v>
       </c>
       <c r="R13" t="n">
-        <v>7396337</v>
+        <v>7396332</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1903,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170126</v>
+        <v>120170110</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>875797</v>
+        <v>876232</v>
       </c>
       <c r="R14" t="n">
-        <v>7396161</v>
+        <v>7396328</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2005,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170107</v>
+        <v>120170109</v>
       </c>
       <c r="B15" t="n">
-        <v>57326</v>
+        <v>79511</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876039</v>
+        <v>875805</v>
       </c>
       <c r="R15" t="n">
-        <v>7396234</v>
+        <v>7396155</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2081,11 +2086,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170111</v>
+        <v>120170104</v>
       </c>
       <c r="B16" t="n">
-        <v>92030</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876267</v>
+        <v>875836</v>
       </c>
       <c r="R16" t="n">
-        <v>7396323</v>
+        <v>7396192</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2188,6 +2188,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170116</v>
+        <v>120170128</v>
       </c>
       <c r="B17" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876017</v>
+        <v>875926</v>
       </c>
       <c r="R17" t="n">
-        <v>7396223</v>
+        <v>7396221</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2418,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170132</v>
+        <v>120170116</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876302</v>
+        <v>876017</v>
       </c>
       <c r="R19" t="n">
-        <v>7396316</v>
+        <v>7396223</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2520,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170104</v>
+        <v>120170101</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,25 +2537,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>875836</v>
+        <v>876264</v>
       </c>
       <c r="R20" t="n">
-        <v>7396192</v>
+        <v>7396337</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2596,11 +2601,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134327</v>
+        <v>120134382</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hanhinoja, Nb</t>
@@ -759,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134333</v>
+        <v>120134335</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876265</v>
+        <v>875839</v>
       </c>
       <c r="R3" t="n">
-        <v>7396339</v>
+        <v>7396189</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +883,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134336</v>
+        <v>120134334</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876268</v>
+        <v>875837</v>
       </c>
       <c r="R4" t="n">
-        <v>7396332</v>
+        <v>7396182</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134382</v>
+        <v>120134327</v>
       </c>
       <c r="B5" t="n">
-        <v>90905</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,31 +997,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hanhinoja, Nb</t>
@@ -1068,7 +1069,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134334</v>
+        <v>120134336</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>875837</v>
+        <v>876268</v>
       </c>
       <c r="R6" t="n">
-        <v>7396182</v>
+        <v>7396332</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134335</v>
+        <v>120134333</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,21 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>875839</v>
+        <v>876265</v>
       </c>
       <c r="R7" t="n">
-        <v>7396189</v>
+        <v>7396339</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120170126</v>
+        <v>120170116</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>875797</v>
+        <v>876017</v>
       </c>
       <c r="R8" t="n">
-        <v>7396161</v>
+        <v>7396223</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170107</v>
+        <v>120170103</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876039</v>
+        <v>876287</v>
       </c>
       <c r="R9" t="n">
-        <v>7396234</v>
+        <v>7396347</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1469,11 +1469,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,7 +1495,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170132</v>
+        <v>120170126</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1540,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876302</v>
+        <v>875797</v>
       </c>
       <c r="R10" t="n">
-        <v>7396316</v>
+        <v>7396161</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1602,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170111</v>
+        <v>120170130</v>
       </c>
       <c r="B11" t="n">
-        <v>92030</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876267</v>
+        <v>876271</v>
       </c>
       <c r="R11" t="n">
-        <v>7396323</v>
+        <v>7396332</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1704,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170103</v>
+        <v>120170107</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
+        <v>57326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876287</v>
+        <v>876039</v>
       </c>
       <c r="R12" t="n">
-        <v>7396347</v>
+        <v>7396234</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1780,6 +1775,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170130</v>
+        <v>120170110</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876271</v>
+        <v>876232</v>
       </c>
       <c r="R13" t="n">
-        <v>7396332</v>
+        <v>7396328</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170110</v>
+        <v>120170101</v>
       </c>
       <c r="B14" t="n">
-        <v>90846</v>
+        <v>90527</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876232</v>
+        <v>876264</v>
       </c>
       <c r="R14" t="n">
-        <v>7396328</v>
+        <v>7396337</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170109</v>
+        <v>120170111</v>
       </c>
       <c r="B15" t="n">
-        <v>79511</v>
+        <v>92030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>875805</v>
+        <v>876267</v>
       </c>
       <c r="R15" t="n">
-        <v>7396155</v>
+        <v>7396323</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170128</v>
+        <v>120170132</v>
       </c>
       <c r="B17" t="n">
         <v>78526</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>875926</v>
+        <v>876302</v>
       </c>
       <c r="R17" t="n">
-        <v>7396221</v>
+        <v>7396316</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170129</v>
+        <v>120170109</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>79511</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,25 +2333,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876188</v>
+        <v>875805</v>
       </c>
       <c r="R18" t="n">
-        <v>7396304</v>
+        <v>7396155</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170116</v>
+        <v>120170129</v>
       </c>
       <c r="B19" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876017</v>
+        <v>876188</v>
       </c>
       <c r="R19" t="n">
-        <v>7396223</v>
+        <v>7396304</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170101</v>
+        <v>120170128</v>
       </c>
       <c r="B20" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,25 +2537,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876264</v>
+        <v>875926</v>
       </c>
       <c r="R20" t="n">
-        <v>7396337</v>
+        <v>7396221</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170104</v>
+        <v>120170132</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>875836</v>
+        <v>876302</v>
       </c>
       <c r="R16" t="n">
-        <v>7396192</v>
+        <v>7396316</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2188,11 +2188,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2219,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170132</v>
+        <v>120170104</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876302</v>
+        <v>875836</v>
       </c>
       <c r="R17" t="n">
-        <v>7396316</v>
+        <v>7396192</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2295,6 +2290,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170103</v>
+        <v>120170126</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876287</v>
+        <v>875797</v>
       </c>
       <c r="R9" t="n">
-        <v>7396347</v>
+        <v>7396161</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170126</v>
+        <v>120170103</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>875797</v>
+        <v>876287</v>
       </c>
       <c r="R10" t="n">
-        <v>7396161</v>
+        <v>7396347</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170132</v>
+        <v>120170104</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876302</v>
+        <v>875836</v>
       </c>
       <c r="R16" t="n">
-        <v>7396316</v>
+        <v>7396192</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2188,6 +2188,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170104</v>
+        <v>120170132</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>875836</v>
+        <v>876302</v>
       </c>
       <c r="R17" t="n">
-        <v>7396192</v>
+        <v>7396316</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2290,11 +2295,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170126</v>
+        <v>120170103</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>875797</v>
+        <v>876287</v>
       </c>
       <c r="R9" t="n">
-        <v>7396161</v>
+        <v>7396347</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170103</v>
+        <v>120170126</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876287</v>
+        <v>875797</v>
       </c>
       <c r="R10" t="n">
-        <v>7396347</v>
+        <v>7396161</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170103</v>
+        <v>120170126</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876287</v>
+        <v>875797</v>
       </c>
       <c r="R9" t="n">
-        <v>7396347</v>
+        <v>7396161</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170126</v>
+        <v>120170103</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>875797</v>
+        <v>876287</v>
       </c>
       <c r="R10" t="n">
-        <v>7396161</v>
+        <v>7396347</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170126</v>
+        <v>120170103</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>875797</v>
+        <v>876287</v>
       </c>
       <c r="R9" t="n">
-        <v>7396161</v>
+        <v>7396347</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170103</v>
+        <v>120170126</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876287</v>
+        <v>875797</v>
       </c>
       <c r="R10" t="n">
-        <v>7396347</v>
+        <v>7396161</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170104</v>
+        <v>120170132</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>875836</v>
+        <v>876302</v>
       </c>
       <c r="R16" t="n">
-        <v>7396192</v>
+        <v>7396316</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2188,11 +2188,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2219,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170132</v>
+        <v>120170104</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876302</v>
+        <v>875836</v>
       </c>
       <c r="R17" t="n">
-        <v>7396316</v>
+        <v>7396192</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2295,6 +2290,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134382</v>
+        <v>120134327</v>
       </c>
       <c r="B2" t="n">
-        <v>90905</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hanhinoja, Nb</t>
@@ -762,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134335</v>
+        <v>120134333</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>875839</v>
+        <v>876265</v>
       </c>
       <c r="R3" t="n">
-        <v>7396189</v>
+        <v>7396339</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -886,7 +882,7 @@
         <v>120134334</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -985,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134327</v>
+        <v>120134335</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876266</v>
+        <v>875839</v>
       </c>
       <c r="R5" t="n">
-        <v>7396336</v>
+        <v>7396189</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1090,7 +1086,7 @@
         <v>120134336</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134333</v>
+        <v>120134382</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,38 +1197,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hanhinoja, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876265</v>
+        <v>876266</v>
       </c>
       <c r="R7" t="n">
-        <v>7396339</v>
+        <v>7396336</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1273,6 +1272,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120170116</v>
+        <v>120170126</v>
       </c>
       <c r="B8" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876017</v>
+        <v>875797</v>
       </c>
       <c r="R8" t="n">
-        <v>7396223</v>
+        <v>7396161</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170103</v>
+        <v>120170101</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,25 +1405,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876287</v>
+        <v>876264</v>
       </c>
       <c r="R9" t="n">
-        <v>7396347</v>
+        <v>7396337</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170126</v>
+        <v>120170109</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>79527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,25 +1507,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>875797</v>
+        <v>875805</v>
       </c>
       <c r="R10" t="n">
-        <v>7396161</v>
+        <v>7396155</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1600,7 +1600,7 @@
         <v>120170130</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170107</v>
+        <v>120170116</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876039</v>
+        <v>876017</v>
       </c>
       <c r="R12" t="n">
-        <v>7396234</v>
+        <v>7396223</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1775,11 +1775,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170110</v>
+        <v>120170104</v>
       </c>
       <c r="B13" t="n">
-        <v>90846</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1817,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876232</v>
+        <v>875836</v>
       </c>
       <c r="R13" t="n">
-        <v>7396328</v>
+        <v>7396192</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1882,6 +1877,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170101</v>
+        <v>120170128</v>
       </c>
       <c r="B14" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876264</v>
+        <v>875926</v>
       </c>
       <c r="R14" t="n">
-        <v>7396337</v>
+        <v>7396221</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170111</v>
+        <v>120170132</v>
       </c>
       <c r="B15" t="n">
-        <v>92030</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876267</v>
+        <v>876302</v>
       </c>
       <c r="R15" t="n">
-        <v>7396323</v>
+        <v>7396316</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170132</v>
+        <v>120170129</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876302</v>
+        <v>876188</v>
       </c>
       <c r="R16" t="n">
-        <v>7396316</v>
+        <v>7396304</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170104</v>
+        <v>120170110</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>90864</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>875836</v>
+        <v>876232</v>
       </c>
       <c r="R17" t="n">
-        <v>7396192</v>
+        <v>7396328</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2290,11 +2290,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2321,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170109</v>
+        <v>120170103</v>
       </c>
       <c r="B18" t="n">
-        <v>79511</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>875805</v>
+        <v>876287</v>
       </c>
       <c r="R18" t="n">
-        <v>7396155</v>
+        <v>7396347</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2423,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170129</v>
+        <v>120170107</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2463,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876188</v>
+        <v>876039</v>
       </c>
       <c r="R19" t="n">
-        <v>7396304</v>
+        <v>7396234</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2499,6 +2494,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2525,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170128</v>
+        <v>120170111</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>92048</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,21 +2541,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>875926</v>
+        <v>876267</v>
       </c>
       <c r="R20" t="n">
-        <v>7396221</v>
+        <v>7396323</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170103</v>
+        <v>120170107</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876287</v>
+        <v>876039</v>
       </c>
       <c r="R18" t="n">
-        <v>7396347</v>
+        <v>7396234</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2392,6 +2392,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170107</v>
+        <v>120170103</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876039</v>
+        <v>876287</v>
       </c>
       <c r="R19" t="n">
-        <v>7396234</v>
+        <v>7396347</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2494,11 +2499,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134327</v>
+        <v>120134382</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hanhinoja, Nb</t>
@@ -759,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134333</v>
+        <v>120134335</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876265</v>
+        <v>875839</v>
       </c>
       <c r="R3" t="n">
-        <v>7396339</v>
+        <v>7396189</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134334</v>
+        <v>120134327</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>875837</v>
+        <v>876266</v>
       </c>
       <c r="R4" t="n">
-        <v>7396182</v>
+        <v>7396336</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,7 +985,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134335</v>
+        <v>120134336</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1021,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>875839</v>
+        <v>876268</v>
       </c>
       <c r="R5" t="n">
-        <v>7396189</v>
+        <v>7396332</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,7 +1087,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134336</v>
+        <v>120134334</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1123,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876268</v>
+        <v>875837</v>
       </c>
       <c r="R6" t="n">
-        <v>7396332</v>
+        <v>7396182</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134382</v>
+        <v>120134333</v>
       </c>
       <c r="B7" t="n">
-        <v>90923</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,41 +1201,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hanhinoja, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876266</v>
+        <v>876265</v>
       </c>
       <c r="R7" t="n">
-        <v>7396336</v>
+        <v>7396339</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1272,7 +1273,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120170126</v>
+        <v>120170103</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>875797</v>
+        <v>876287</v>
       </c>
       <c r="R8" t="n">
-        <v>7396161</v>
+        <v>7396347</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170101</v>
+        <v>120170130</v>
       </c>
       <c r="B9" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,25 +1405,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876264</v>
+        <v>876271</v>
       </c>
       <c r="R9" t="n">
-        <v>7396337</v>
+        <v>7396332</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170109</v>
+        <v>120170111</v>
       </c>
       <c r="B10" t="n">
-        <v>79527</v>
+        <v>92048</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,25 +1507,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>875805</v>
+        <v>876267</v>
       </c>
       <c r="R10" t="n">
-        <v>7396155</v>
+        <v>7396323</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170130</v>
+        <v>120170110</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876271</v>
+        <v>876232</v>
       </c>
       <c r="R11" t="n">
-        <v>7396332</v>
+        <v>7396328</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170104</v>
+        <v>120170126</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>875836</v>
+        <v>875797</v>
       </c>
       <c r="R13" t="n">
-        <v>7396192</v>
+        <v>7396161</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1877,11 +1877,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1908,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170128</v>
+        <v>120170107</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>875926</v>
+        <v>876039</v>
       </c>
       <c r="R14" t="n">
-        <v>7396221</v>
+        <v>7396234</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1984,6 +1979,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2010,7 +2010,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170132</v>
+        <v>120170128</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876302</v>
+        <v>875926</v>
       </c>
       <c r="R15" t="n">
-        <v>7396316</v>
+        <v>7396221</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170129</v>
+        <v>120170104</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876188</v>
+        <v>875836</v>
       </c>
       <c r="R16" t="n">
-        <v>7396304</v>
+        <v>7396192</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2188,6 +2188,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170110</v>
+        <v>120170109</v>
       </c>
       <c r="B17" t="n">
-        <v>90864</v>
+        <v>79527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,25 +2231,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876232</v>
+        <v>875805</v>
       </c>
       <c r="R17" t="n">
-        <v>7396328</v>
+        <v>7396155</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2316,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170107</v>
+        <v>120170101</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>90545</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,25 +2333,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876039</v>
+        <v>876264</v>
       </c>
       <c r="R18" t="n">
-        <v>7396234</v>
+        <v>7396337</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2392,11 +2397,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170103</v>
+        <v>120170132</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876287</v>
+        <v>876302</v>
       </c>
       <c r="R19" t="n">
-        <v>7396347</v>
+        <v>7396316</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170111</v>
+        <v>120170129</v>
       </c>
       <c r="B20" t="n">
-        <v>92048</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,21 +2541,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876267</v>
+        <v>876188</v>
       </c>
       <c r="R20" t="n">
-        <v>7396323</v>
+        <v>7396304</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170128</v>
+        <v>120170104</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>875926</v>
+        <v>875836</v>
       </c>
       <c r="R15" t="n">
-        <v>7396221</v>
+        <v>7396192</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2086,6 +2086,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2112,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170104</v>
+        <v>120170128</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2133,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>875836</v>
+        <v>875926</v>
       </c>
       <c r="R16" t="n">
-        <v>7396192</v>
+        <v>7396221</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2188,11 +2193,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134382</v>
+        <v>120134335</v>
       </c>
       <c r="B2" t="n">
-        <v>90923</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hanhinoja, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876266</v>
+        <v>875839</v>
       </c>
       <c r="R2" t="n">
-        <v>7396336</v>
+        <v>7396189</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -762,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134335</v>
+        <v>120134336</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>875839</v>
+        <v>876268</v>
       </c>
       <c r="R3" t="n">
-        <v>7396189</v>
+        <v>7396332</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -883,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134327</v>
+        <v>120134333</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876266</v>
+        <v>876265</v>
       </c>
       <c r="R4" t="n">
-        <v>7396336</v>
+        <v>7396339</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -985,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134336</v>
+        <v>120134382</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90923</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,38 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hanhinoja, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876268</v>
+        <v>876266</v>
       </c>
       <c r="R5" t="n">
-        <v>7396332</v>
+        <v>7396336</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1069,6 +1068,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134333</v>
+        <v>120134327</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,21 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876265</v>
+        <v>876266</v>
       </c>
       <c r="R7" t="n">
-        <v>7396339</v>
+        <v>7396336</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120170103</v>
+        <v>120170126</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876287</v>
+        <v>875797</v>
       </c>
       <c r="R8" t="n">
-        <v>7396347</v>
+        <v>7396161</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170130</v>
+        <v>120170107</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876271</v>
+        <v>876039</v>
       </c>
       <c r="R9" t="n">
-        <v>7396332</v>
+        <v>7396234</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1469,6 +1469,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170111</v>
+        <v>120170109</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>79527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876267</v>
+        <v>875805</v>
       </c>
       <c r="R10" t="n">
-        <v>7396323</v>
+        <v>7396155</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1597,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170110</v>
+        <v>120170101</v>
       </c>
       <c r="B11" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876232</v>
+        <v>876264</v>
       </c>
       <c r="R11" t="n">
-        <v>7396328</v>
+        <v>7396337</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1699,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170116</v>
+        <v>120170130</v>
       </c>
       <c r="B12" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876017</v>
+        <v>876271</v>
       </c>
       <c r="R12" t="n">
-        <v>7396223</v>
+        <v>7396332</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1801,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170126</v>
+        <v>120170104</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>875797</v>
+        <v>875836</v>
       </c>
       <c r="R13" t="n">
-        <v>7396161</v>
+        <v>7396192</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1877,6 +1882,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1903,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170107</v>
+        <v>120170129</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,21 +1929,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876039</v>
+        <v>876188</v>
       </c>
       <c r="R14" t="n">
-        <v>7396234</v>
+        <v>7396304</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1979,11 +1989,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2010,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170104</v>
+        <v>120170103</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2031,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>875836</v>
+        <v>876287</v>
       </c>
       <c r="R15" t="n">
-        <v>7396192</v>
+        <v>7396347</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2086,11 +2091,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2117,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170128</v>
+        <v>120170110</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,21 +2133,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>875926</v>
+        <v>876232</v>
       </c>
       <c r="R16" t="n">
-        <v>7396221</v>
+        <v>7396328</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170109</v>
+        <v>120170128</v>
       </c>
       <c r="B17" t="n">
-        <v>79527</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>875805</v>
+        <v>875926</v>
       </c>
       <c r="R17" t="n">
-        <v>7396155</v>
+        <v>7396221</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170101</v>
+        <v>120170116</v>
       </c>
       <c r="B18" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,25 +2333,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876264</v>
+        <v>876017</v>
       </c>
       <c r="R18" t="n">
-        <v>7396337</v>
+        <v>7396223</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170129</v>
+        <v>120170111</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,21 +2541,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876188</v>
+        <v>876267</v>
       </c>
       <c r="R20" t="n">
-        <v>7396304</v>
+        <v>7396323</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -2117,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170110</v>
+        <v>120170128</v>
       </c>
       <c r="B16" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,21 +2133,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876232</v>
+        <v>875926</v>
       </c>
       <c r="R16" t="n">
-        <v>7396328</v>
+        <v>7396221</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170128</v>
+        <v>120170116</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>875926</v>
+        <v>876017</v>
       </c>
       <c r="R17" t="n">
-        <v>7396221</v>
+        <v>7396223</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170116</v>
+        <v>120170110</v>
       </c>
       <c r="B18" t="n">
-        <v>78278</v>
+        <v>90864</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876017</v>
+        <v>876232</v>
       </c>
       <c r="R18" t="n">
-        <v>7396223</v>
+        <v>7396328</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134335</v>
+        <v>120134327</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>875839</v>
+        <v>876266</v>
       </c>
       <c r="R2" t="n">
-        <v>7396189</v>
+        <v>7396336</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134336</v>
+        <v>120134333</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876268</v>
+        <v>876265</v>
       </c>
       <c r="R3" t="n">
-        <v>7396332</v>
+        <v>7396339</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134333</v>
+        <v>120134334</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876265</v>
+        <v>875837</v>
       </c>
       <c r="R4" t="n">
-        <v>7396339</v>
+        <v>7396182</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134334</v>
+        <v>120134336</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>875837</v>
+        <v>876268</v>
       </c>
       <c r="R6" t="n">
-        <v>7396182</v>
+        <v>7396332</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134327</v>
+        <v>120134335</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,21 +1205,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876266</v>
+        <v>875839</v>
       </c>
       <c r="R7" t="n">
-        <v>7396336</v>
+        <v>7396189</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120170126</v>
+        <v>120170128</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>875797</v>
+        <v>875926</v>
       </c>
       <c r="R8" t="n">
-        <v>7396161</v>
+        <v>7396221</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170107</v>
+        <v>120170110</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>90864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876039</v>
+        <v>876232</v>
       </c>
       <c r="R9" t="n">
-        <v>7396234</v>
+        <v>7396328</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1469,11 +1469,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170109</v>
+        <v>120170101</v>
       </c>
       <c r="B10" t="n">
-        <v>79527</v>
+        <v>90545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>875805</v>
+        <v>876264</v>
       </c>
       <c r="R10" t="n">
-        <v>7396155</v>
+        <v>7396337</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1602,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170101</v>
+        <v>120170132</v>
       </c>
       <c r="B11" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1609,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876264</v>
+        <v>876302</v>
       </c>
       <c r="R11" t="n">
-        <v>7396337</v>
+        <v>7396316</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1704,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170130</v>
+        <v>120170107</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876271</v>
+        <v>876039</v>
       </c>
       <c r="R12" t="n">
-        <v>7396332</v>
+        <v>7396234</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1780,6 +1775,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170104</v>
+        <v>120170129</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>875836</v>
+        <v>876188</v>
       </c>
       <c r="R13" t="n">
-        <v>7396192</v>
+        <v>7396304</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1882,11 +1882,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1913,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170129</v>
+        <v>120170116</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1953,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876188</v>
+        <v>876017</v>
       </c>
       <c r="R14" t="n">
-        <v>7396304</v>
+        <v>7396223</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2015,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170103</v>
+        <v>120170130</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2031,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876287</v>
+        <v>876271</v>
       </c>
       <c r="R15" t="n">
-        <v>7396347</v>
+        <v>7396332</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2117,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170128</v>
+        <v>120170109</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79527</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2157,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>875926</v>
+        <v>875805</v>
       </c>
       <c r="R16" t="n">
-        <v>7396221</v>
+        <v>7396155</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2219,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170116</v>
+        <v>120170104</v>
       </c>
       <c r="B17" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876017</v>
+        <v>875836</v>
       </c>
       <c r="R17" t="n">
-        <v>7396223</v>
+        <v>7396192</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2295,6 +2290,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170110</v>
+        <v>120170103</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876232</v>
+        <v>876287</v>
       </c>
       <c r="R18" t="n">
-        <v>7396328</v>
+        <v>7396347</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170132</v>
+        <v>120170111</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876302</v>
+        <v>876267</v>
       </c>
       <c r="R19" t="n">
-        <v>7396316</v>
+        <v>7396323</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170111</v>
+        <v>120170126</v>
       </c>
       <c r="B20" t="n">
-        <v>92048</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,21 +2541,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876267</v>
+        <v>875797</v>
       </c>
       <c r="R20" t="n">
-        <v>7396323</v>
+        <v>7396161</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134327</v>
+        <v>120134334</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>876266</v>
+        <v>875837</v>
       </c>
       <c r="R2" t="n">
-        <v>7396336</v>
+        <v>7396182</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134333</v>
+        <v>120134335</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876265</v>
+        <v>875839</v>
       </c>
       <c r="R3" t="n">
-        <v>7396339</v>
+        <v>7396189</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134334</v>
+        <v>120134327</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>875837</v>
+        <v>876266</v>
       </c>
       <c r="R4" t="n">
-        <v>7396182</v>
+        <v>7396336</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134382</v>
+        <v>120134333</v>
       </c>
       <c r="B5" t="n">
-        <v>90923</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hanhinoja, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876266</v>
+        <v>876265</v>
       </c>
       <c r="R5" t="n">
-        <v>7396336</v>
+        <v>7396339</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1068,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1189,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134335</v>
+        <v>120134382</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>90923</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,38 +1197,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hanhinoja, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>875839</v>
+        <v>876266</v>
       </c>
       <c r="R7" t="n">
-        <v>7396189</v>
+        <v>7396336</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1273,6 +1272,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120170128</v>
+        <v>120170110</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>875926</v>
+        <v>876232</v>
       </c>
       <c r="R8" t="n">
-        <v>7396221</v>
+        <v>7396328</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170110</v>
+        <v>120170126</v>
       </c>
       <c r="B9" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876232</v>
+        <v>875797</v>
       </c>
       <c r="R9" t="n">
-        <v>7396328</v>
+        <v>7396161</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1597,7 +1597,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170132</v>
+        <v>120170129</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876302</v>
+        <v>876188</v>
       </c>
       <c r="R11" t="n">
-        <v>7396316</v>
+        <v>7396304</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170129</v>
+        <v>120170103</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876188</v>
+        <v>876287</v>
       </c>
       <c r="R13" t="n">
-        <v>7396304</v>
+        <v>7396347</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170116</v>
+        <v>120170130</v>
       </c>
       <c r="B14" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876017</v>
+        <v>876271</v>
       </c>
       <c r="R14" t="n">
-        <v>7396223</v>
+        <v>7396332</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170130</v>
+        <v>120170111</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876271</v>
+        <v>876267</v>
       </c>
       <c r="R15" t="n">
-        <v>7396332</v>
+        <v>7396323</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170109</v>
+        <v>120170116</v>
       </c>
       <c r="B16" t="n">
-        <v>79527</v>
+        <v>78278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>875805</v>
+        <v>876017</v>
       </c>
       <c r="R16" t="n">
-        <v>7396155</v>
+        <v>7396223</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170103</v>
+        <v>120170128</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>876287</v>
+        <v>875926</v>
       </c>
       <c r="R18" t="n">
-        <v>7396347</v>
+        <v>7396221</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170111</v>
+        <v>120170132</v>
       </c>
       <c r="B19" t="n">
-        <v>92048</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876267</v>
+        <v>876302</v>
       </c>
       <c r="R19" t="n">
-        <v>7396323</v>
+        <v>7396316</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170126</v>
+        <v>120170109</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>79527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,25 +2537,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>875797</v>
+        <v>875805</v>
       </c>
       <c r="R20" t="n">
-        <v>7396161</v>
+        <v>7396155</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170116</v>
+        <v>120170104</v>
       </c>
       <c r="B16" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>876017</v>
+        <v>875836</v>
       </c>
       <c r="R16" t="n">
-        <v>7396223</v>
+        <v>7396192</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2188,6 +2188,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170104</v>
+        <v>120170116</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>875836</v>
+        <v>876017</v>
       </c>
       <c r="R17" t="n">
-        <v>7396192</v>
+        <v>7396223</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2290,11 +2295,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120134334</v>
+        <v>120134336</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>875837</v>
+        <v>876268</v>
       </c>
       <c r="R2" t="n">
-        <v>7396182</v>
+        <v>7396332</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134335</v>
+        <v>120134333</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>875839</v>
+        <v>876265</v>
       </c>
       <c r="R3" t="n">
-        <v>7396189</v>
+        <v>7396339</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134333</v>
+        <v>120134334</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>876265</v>
+        <v>875837</v>
       </c>
       <c r="R5" t="n">
-        <v>7396339</v>
+        <v>7396182</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134336</v>
+        <v>120134335</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>876268</v>
+        <v>875839</v>
       </c>
       <c r="R6" t="n">
-        <v>7396332</v>
+        <v>7396189</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120170110</v>
+        <v>120170101</v>
       </c>
       <c r="B8" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,25 +1303,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>876232</v>
+        <v>876264</v>
       </c>
       <c r="R8" t="n">
-        <v>7396328</v>
+        <v>7396337</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170126</v>
+        <v>120170103</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>875797</v>
+        <v>876287</v>
       </c>
       <c r="R9" t="n">
-        <v>7396161</v>
+        <v>7396347</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170101</v>
+        <v>120170116</v>
       </c>
       <c r="B10" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,25 +1507,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876264</v>
+        <v>876017</v>
       </c>
       <c r="R10" t="n">
-        <v>7396337</v>
+        <v>7396223</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170129</v>
+        <v>120170111</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876188</v>
+        <v>876267</v>
       </c>
       <c r="R11" t="n">
-        <v>7396304</v>
+        <v>7396323</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170107</v>
+        <v>120170132</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876039</v>
+        <v>876302</v>
       </c>
       <c r="R12" t="n">
-        <v>7396234</v>
+        <v>7396316</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1775,11 +1775,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170103</v>
+        <v>120170126</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1817,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>876287</v>
+        <v>875797</v>
       </c>
       <c r="R13" t="n">
-        <v>7396347</v>
+        <v>7396161</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1908,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170130</v>
+        <v>120170110</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876271</v>
+        <v>876232</v>
       </c>
       <c r="R14" t="n">
-        <v>7396332</v>
+        <v>7396328</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2010,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170111</v>
+        <v>120170107</v>
       </c>
       <c r="B15" t="n">
-        <v>92048</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2021,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876267</v>
+        <v>876039</v>
       </c>
       <c r="R15" t="n">
-        <v>7396323</v>
+        <v>7396234</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2086,6 +2081,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120170104</v>
+        <v>120170130</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>875836</v>
+        <v>876271</v>
       </c>
       <c r="R16" t="n">
-        <v>7396192</v>
+        <v>7396332</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2188,11 +2188,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2219,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170116</v>
+        <v>120170104</v>
       </c>
       <c r="B17" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>876017</v>
+        <v>875836</v>
       </c>
       <c r="R17" t="n">
-        <v>7396223</v>
+        <v>7396192</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2295,6 +2290,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170128</v>
+        <v>120170109</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>79527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,25 +2333,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>875926</v>
+        <v>875805</v>
       </c>
       <c r="R18" t="n">
-        <v>7396221</v>
+        <v>7396155</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120170132</v>
+        <v>120170128</v>
       </c>
       <c r="B19" t="n">
         <v>78542</v>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>876302</v>
+        <v>875926</v>
       </c>
       <c r="R19" t="n">
-        <v>7396316</v>
+        <v>7396221</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170109</v>
+        <v>120170129</v>
       </c>
       <c r="B20" t="n">
-        <v>79527</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,25 +2537,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>875805</v>
+        <v>876188</v>
       </c>
       <c r="R20" t="n">
-        <v>7396155</v>
+        <v>7396304</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>

--- a/artfynd/A 41916-2024 artfynd.xlsx
+++ b/artfynd/A 41916-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120134333</v>
+        <v>120134382</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>90923</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hanhinoja, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876265</v>
+        <v>876266</v>
       </c>
       <c r="R3" t="n">
-        <v>7396339</v>
+        <v>7396336</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -861,6 +864,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120134327</v>
+        <v>120134335</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>876266</v>
+        <v>875839</v>
       </c>
       <c r="R4" t="n">
-        <v>7396336</v>
+        <v>7396189</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120134334</v>
+        <v>120134333</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>875837</v>
+        <v>876265</v>
       </c>
       <c r="R5" t="n">
-        <v>7396182</v>
+        <v>7396339</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120134335</v>
+        <v>120134327</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>875839</v>
+        <v>876266</v>
       </c>
       <c r="R6" t="n">
-        <v>7396189</v>
+        <v>7396336</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120134382</v>
+        <v>120134334</v>
       </c>
       <c r="B7" t="n">
-        <v>90923</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,41 +1201,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hanhinoja, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>876266</v>
+        <v>875837</v>
       </c>
       <c r="R7" t="n">
-        <v>7396336</v>
+        <v>7396182</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1272,7 +1273,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120170103</v>
+        <v>120170129</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>876287</v>
+        <v>876188</v>
       </c>
       <c r="R9" t="n">
-        <v>7396347</v>
+        <v>7396304</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120170116</v>
+        <v>120170104</v>
       </c>
       <c r="B10" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>876017</v>
+        <v>875836</v>
       </c>
       <c r="R10" t="n">
-        <v>7396223</v>
+        <v>7396192</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1571,6 +1571,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120170111</v>
+        <v>120170110</v>
       </c>
       <c r="B11" t="n">
-        <v>92048</v>
+        <v>90864</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>876267</v>
+        <v>876232</v>
       </c>
       <c r="R11" t="n">
-        <v>7396323</v>
+        <v>7396328</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1699,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120170132</v>
+        <v>120170103</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>876302</v>
+        <v>876287</v>
       </c>
       <c r="R12" t="n">
-        <v>7396316</v>
+        <v>7396347</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1801,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120170126</v>
+        <v>120170109</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>79527</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>875797</v>
+        <v>875805</v>
       </c>
       <c r="R13" t="n">
-        <v>7396161</v>
+        <v>7396155</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1903,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120170110</v>
+        <v>120170126</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>876232</v>
+        <v>875797</v>
       </c>
       <c r="R14" t="n">
-        <v>7396328</v>
+        <v>7396161</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2005,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120170107</v>
+        <v>120170111</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>92048</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2021,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>876039</v>
+        <v>876267</v>
       </c>
       <c r="R15" t="n">
-        <v>7396234</v>
+        <v>7396323</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2081,11 +2086,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120170104</v>
+        <v>120170132</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>875836</v>
+        <v>876302</v>
       </c>
       <c r="R17" t="n">
-        <v>7396192</v>
+        <v>7396316</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2290,11 +2290,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2321,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120170109</v>
+        <v>120170107</v>
       </c>
       <c r="B18" t="n">
-        <v>79527</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>875805</v>
+        <v>876039</v>
       </c>
       <c r="R18" t="n">
-        <v>7396155</v>
+        <v>7396234</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2397,6 +2392,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>avbarkad tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2525,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120170129</v>
+        <v>120170116</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,21 +2541,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>876188</v>
+        <v>876017</v>
       </c>
       <c r="R20" t="n">
-        <v>7396304</v>
+        <v>7396223</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
